--- a/docs/engineering-change/design-change/设计变更导入_青岛_T28模版 增加二级 一级变更.xlsx
+++ b/docs/engineering-change/design-change/设计变更导入_青岛_T28模版 增加二级 一级变更.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zhang\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\高考\stamping-costing-platform\docs\engineering-change\design-change\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EEC3B42-C375-4588-8EAE-96FF51FEABB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{972885D3-B625-426C-A519-98094A71F15E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33480" yWindow="-120" windowWidth="19440" windowHeight="10320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33480" yWindow="-120" windowWidth="19440" windowHeight="10320" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="设计变更单" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="173">
   <si>
     <t>设计变更单</t>
   </si>
@@ -540,6 +540,24 @@
   </si>
   <si>
     <t>增加分总成</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>中通道后纵梁本体II</t>
+  </si>
+  <si>
+    <t>前排气管吊钩总成</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>501005057AB</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>ACA611010</t>
+  </si>
+  <si>
+    <t>/</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -759,7 +777,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -810,9 +828,6 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -820,11 +835,20 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -837,15 +861,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1089,7 +1104,7 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="323850" cy="304800"/>
@@ -1129,7 +1144,7 @@
     <xdr:from>
       <xdr:col>15</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="342900" cy="342900"/>
@@ -1296,7 +1311,7 @@
       <xdr:col>4</xdr:col>
       <xdr:colOff>342900</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
+      <xdr:rowOff>63500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1346,6 +1361,147 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1025" name="Image 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E23B81C5-7734-2A61-8345-37E6FE0969AA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3911600" y="1085850"/>
+          <a:ext cx="342900" cy="342900"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="323850" cy="304800"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="Image 4" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{39EA9489-E6DD-40A0-80E4-1618301845AE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3914775" y="2743200"/>
+          <a:ext cx="323850" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="342900" cy="342900"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="Image 6" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8AC70380-C499-4A22-A3AA-7770DB26CE9C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14735175" y="2743200"/>
+          <a:ext cx="342900" cy="342900"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1814,7 +1970,7 @@
       <c r="I1" s="15"/>
       <c r="J1" s="15"/>
     </row>
-    <row r="2" spans="1:10" ht="150" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="17" t="s">
         <v>1</v>
       </c>
@@ -2018,7 +2174,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="15"/>
       <c r="B11" s="13"/>
       <c r="C11" s="19"/>
@@ -2027,39 +2183,38 @@
         <v>43</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>167</v>
+        <v>42</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>158</v>
+        <v>29</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="15"/>
       <c r="B12" s="13"/>
-      <c r="C12" s="20"/>
-      <c r="D12" s="20"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
       <c r="E12" s="4" t="s">
         <v>43</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>42</v>
+        <v>167</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="H12" s="4"/>
       <c r="I12" s="4" t="s">
-        <v>44</v>
+        <v>156</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>45</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>
@@ -2097,7 +2252,7 @@
       <c r="F1" s="15"/>
     </row>
     <row r="2" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="20" t="s">
         <v>47</v>
       </c>
       <c r="B2" s="15"/>
@@ -2107,7 +2262,7 @@
       <c r="F2" s="15"/>
     </row>
     <row r="3" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="20" t="s">
         <v>48</v>
       </c>
       <c r="B3" s="15"/>
@@ -2117,7 +2272,7 @@
       <c r="F3" s="15"/>
     </row>
     <row r="4" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="20" t="s">
         <v>49</v>
       </c>
       <c r="B4" s="15"/>
@@ -2127,7 +2282,7 @@
       <c r="F4" s="15"/>
     </row>
     <row r="5" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="20" t="s">
         <v>50</v>
       </c>
       <c r="B5" s="15"/>
@@ -2137,7 +2292,7 @@
       <c r="F5" s="15"/>
     </row>
     <row r="6" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="20" t="s">
         <v>51</v>
       </c>
       <c r="B6" s="15"/>
@@ -2147,7 +2302,7 @@
       <c r="F6" s="15"/>
     </row>
     <row r="7" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="20" t="s">
         <v>52</v>
       </c>
       <c r="B7" s="15"/>
@@ -2172,8 +2327,8 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:W11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:W12"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="12" customWidth="1"/>
@@ -2181,13 +2336,14 @@
     <col min="5" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="16.90625" customWidth="1"/>
     <col min="10" max="10" width="22" customWidth="1"/>
-    <col min="11" max="14" width="12" customWidth="1"/>
+    <col min="11" max="13" width="12" customWidth="1"/>
+    <col min="14" max="14" width="19.26953125" customWidth="1"/>
     <col min="15" max="15" width="20" customWidth="1"/>
     <col min="16" max="23" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="26" t="s">
         <v>53</v>
       </c>
       <c r="B1" s="15"/>
@@ -2605,23 +2761,23 @@
       <c r="W8" s="8"/>
     </row>
     <row r="9" spans="1:23" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="31">
+      <c r="A9" s="23">
         <v>5</v>
       </c>
-      <c r="B9" s="31" t="s">
+      <c r="B9" s="23" t="s">
         <v>162</v>
       </c>
-      <c r="C9" s="31" t="s">
+      <c r="C9" s="23" t="s">
         <v>160</v>
       </c>
-      <c r="D9" s="31" t="s">
+      <c r="D9" s="23" t="s">
         <v>161</v>
       </c>
-      <c r="E9" s="31"/>
-      <c r="F9" s="31">
+      <c r="E9" s="23"/>
+      <c r="F9" s="23">
         <v>1</v>
       </c>
-      <c r="G9" s="31" t="s">
+      <c r="G9" s="23" t="s">
         <v>163</v>
       </c>
       <c r="H9" s="7" t="s">
@@ -2669,131 +2825,181 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:23" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="32"/>
-      <c r="B10" s="32"/>
-      <c r="C10" s="32"/>
-      <c r="D10" s="32" t="s">
-        <v>161</v>
-      </c>
-      <c r="E10" s="32"/>
-      <c r="F10" s="32">
+    <row r="10" spans="1:23" ht="21.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="24"/>
+      <c r="B10" s="24"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="24"/>
+      <c r="H10" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="K10" s="7">
         <v>1</v>
       </c>
-      <c r="G10" s="32" t="s">
-        <v>163</v>
-      </c>
-      <c r="H10" s="24" t="s">
-        <v>110</v>
-      </c>
-      <c r="I10" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="J10" s="22" t="s">
-        <v>112</v>
-      </c>
-      <c r="K10" s="24" t="s">
-        <v>86</v>
-      </c>
-      <c r="L10" s="24" t="s">
-        <v>87</v>
+      <c r="L10" s="7" t="s">
+        <v>172</v>
       </c>
       <c r="M10" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="N10" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="O10" s="4" t="s">
-        <v>45</v>
+      <c r="N10" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>168</v>
       </c>
       <c r="P10" s="8"/>
       <c r="Q10" s="8">
         <v>1</v>
       </c>
       <c r="R10" s="8" t="s">
-        <v>109</v>
+        <v>164</v>
       </c>
       <c r="S10" s="8" t="s">
-        <v>104</v>
+        <v>165</v>
       </c>
       <c r="T10" s="8"/>
       <c r="U10" s="8">
-        <v>0.23499999999999999</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="V10" s="8" t="s">
         <v>87</v>
       </c>
       <c r="W10" s="8"/>
     </row>
-    <row r="11" spans="1:23" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="33"/>
-      <c r="B11" s="33"/>
-      <c r="C11" s="33"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="33"/>
-      <c r="F11" s="33"/>
-      <c r="G11" s="33"/>
-      <c r="H11" s="23"/>
-      <c r="I11" s="23"/>
-      <c r="J11" s="23"/>
-      <c r="K11" s="23"/>
-      <c r="L11" s="23"/>
+    <row r="11" spans="1:23" ht="21.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="24"/>
+      <c r="B11" s="24"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="E11" s="24"/>
+      <c r="F11" s="24">
+        <v>1</v>
+      </c>
+      <c r="G11" s="24" t="s">
+        <v>163</v>
+      </c>
+      <c r="H11" s="27" t="s">
+        <v>110</v>
+      </c>
+      <c r="I11" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="J11" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="K11" s="27" t="s">
+        <v>86</v>
+      </c>
+      <c r="L11" s="27" t="s">
+        <v>87</v>
+      </c>
       <c r="M11" s="8" t="s">
-        <v>113</v>
+        <v>87</v>
       </c>
       <c r="N11" s="4" t="s">
-        <v>114</v>
+        <v>44</v>
       </c>
       <c r="O11" s="4" t="s">
-        <v>157</v>
+        <v>45</v>
       </c>
       <c r="P11" s="8"/>
       <c r="Q11" s="8">
         <v>1</v>
       </c>
       <c r="R11" s="8" t="s">
-        <v>164</v>
+        <v>109</v>
       </c>
       <c r="S11" s="8" t="s">
-        <v>165</v>
+        <v>104</v>
       </c>
       <c r="T11" s="8"/>
       <c r="U11" s="8">
+        <v>0.23499999999999999</v>
+      </c>
+      <c r="V11" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="W11" s="8"/>
+    </row>
+    <row r="12" spans="1:23" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="25"/>
+      <c r="B12" s="25"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="25"/>
+      <c r="G12" s="25"/>
+      <c r="H12" s="22"/>
+      <c r="I12" s="22"/>
+      <c r="J12" s="22"/>
+      <c r="K12" s="22"/>
+      <c r="L12" s="22"/>
+      <c r="M12" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="N12" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="O12" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="P12" s="8"/>
+      <c r="Q12" s="8">
+        <v>1</v>
+      </c>
+      <c r="R12" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="S12" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="T12" s="8"/>
+      <c r="U12" s="8">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="V11" s="8" t="s">
+      <c r="V12" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="W11" s="8"/>
+      <c r="W12" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="V3:W3"/>
+    <mergeCell ref="R3:U3"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="F9:F12"/>
+    <mergeCell ref="G9:G12"/>
+    <mergeCell ref="E9:E12"/>
     <mergeCell ref="A1:W1"/>
     <mergeCell ref="N3:O3"/>
     <mergeCell ref="I3:M3"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="L10:L11"/>
+    <mergeCell ref="L11:L12"/>
     <mergeCell ref="A2:W2"/>
     <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="D9:D11"/>
-    <mergeCell ref="I10:I11"/>
-    <mergeCell ref="K10:K11"/>
-    <mergeCell ref="V3:W3"/>
-    <mergeCell ref="R3:U3"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="J10:J11"/>
-    <mergeCell ref="F9:F11"/>
-    <mergeCell ref="G9:G11"/>
-    <mergeCell ref="E9:E11"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="A9:A12"/>
+    <mergeCell ref="C9:C12"/>
+    <mergeCell ref="D9:D12"/>
+    <mergeCell ref="I11:I12"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -2865,7 +3071,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:20" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D2" s="28" t="s">
+      <c r="D2" s="30" t="s">
         <v>121</v>
       </c>
       <c r="E2" s="15"/>
@@ -2892,68 +3098,68 @@
       </c>
       <c r="E3" s="15"/>
       <c r="F3" s="15"/>
-      <c r="Q3" s="26" t="s">
+      <c r="Q3" s="28" t="s">
         <v>124</v>
       </c>
       <c r="R3" s="15"/>
-      <c r="S3" s="26" t="s">
+      <c r="S3" s="28" t="s">
         <v>125</v>
       </c>
       <c r="T3" s="15"/>
     </row>
     <row r="5" spans="1:20" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="B5" s="27" t="s">
+      <c r="B5" s="29" t="s">
         <v>126</v>
       </c>
-      <c r="C5" s="27" t="s">
+      <c r="C5" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="27" t="s">
+      <c r="D5" s="29" t="s">
         <v>127</v>
       </c>
-      <c r="E5" s="27" t="s">
+      <c r="E5" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="F5" s="27" t="s">
+      <c r="F5" s="29" t="s">
         <v>129</v>
       </c>
-      <c r="G5" s="27" t="s">
+      <c r="G5" s="29" t="s">
         <v>130</v>
       </c>
-      <c r="H5" s="27" t="s">
+      <c r="H5" s="29" t="s">
         <v>131</v>
       </c>
-      <c r="I5" s="29"/>
-      <c r="J5" s="29"/>
-      <c r="K5" s="29"/>
-      <c r="L5" s="29"/>
-      <c r="M5" s="30"/>
-      <c r="N5" s="27" t="s">
+      <c r="I5" s="31"/>
+      <c r="J5" s="31"/>
+      <c r="K5" s="31"/>
+      <c r="L5" s="31"/>
+      <c r="M5" s="32"/>
+      <c r="N5" s="29" t="s">
         <v>132</v>
       </c>
-      <c r="O5" s="29"/>
-      <c r="P5" s="30"/>
-      <c r="Q5" s="27" t="s">
+      <c r="O5" s="31"/>
+      <c r="P5" s="32"/>
+      <c r="Q5" s="29" t="s">
         <v>133</v>
       </c>
-      <c r="R5" s="27" t="s">
+      <c r="R5" s="29" t="s">
         <v>134</v>
       </c>
-      <c r="S5" s="27" t="s">
+      <c r="S5" s="29" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="23"/>
-      <c r="B6" s="23"/>
-      <c r="C6" s="23"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="23"/>
-      <c r="G6" s="23"/>
+      <c r="A6" s="22"/>
+      <c r="B6" s="22"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="22"/>
       <c r="H6" s="11" t="s">
         <v>136</v>
       </c>
@@ -2981,9 +3187,9 @@
       <c r="P6" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="Q6" s="23"/>
-      <c r="R6" s="23"/>
-      <c r="S6" s="23"/>
+      <c r="Q6" s="22"/>
+      <c r="R6" s="22"/>
+      <c r="S6" s="22"/>
     </row>
     <row r="7" spans="1:20" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
